--- a/p6_deployment/data/italy/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/italy/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2230,66 +2230,418 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Oj506F56</t>
+          <t>CMCRCR04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>KrUMD1Kd</t>
+          <t>KnGZA5VG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>dh7TdRoQ</t>
+          <t>hM5FFTGo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>GE9r9q0T</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>vJHXjpvo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>j7OIEmWi</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>tdHVBoGA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>YVDND7ob</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>YgdA438p</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2B5vAPpN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>C2pt1U1h</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>nLxgbSoB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>xAV5eQVT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>jgqp0lHb</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>4xox2Ann</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>trxccn1H</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>YHYla8W4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>KYz1d6GN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>QonY2jXu</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
